--- a/apps/web/public/templates/phieu-thu-tien-template.xlsx
+++ b/apps/web/public/templates/phieu-thu-tien-template.xlsx
@@ -572,6 +572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
+    <x:pageSetUpPr fitToPage="1"/>
     <x:tabColor rgb="FF5546E8"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1086,7 +1087,8 @@
     <x:mergeCell ref="G30:H30"/>
     <x:mergeCell ref="A32:I32"/>
   </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <x:pageSetup paperSize="11" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R775ba4fddc364177"/>
 </x:worksheet>
 </file>
--- a/apps/web/public/templates/phieu-thu-tien-template.xlsx
+++ b/apps/web/public/templates/phieu-thu-tien-template.xlsx
@@ -355,7 +355,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="552450" cy="552450"/>
+    <xdr:ext cx="807424" cy="552450"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="3ee82e52-48a6-4072-ac02-bd0abf7e5908"/>
@@ -968,7 +968,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="46" t="str">
-        <x:v>Cảm ơn quý khách đã sử dụng dịch vụ tại DentalERP.</x:v>
+        <x:v>Cảm ơn quý khách đã sử dụng dịch vụ tại DentalKhoi.</x:v>
       </x:c>
       <x:c r="B32" s="46"/>
       <x:c r="C32" s="46"/>
